--- a/archivos/tabla_variedades.xlsx
+++ b/archivos/tabla_variedades.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTICA\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE3970BF-0BBB-4C82-8B96-A8F154ACE420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969D51BC-FF0F-4EBF-A690-459F569BA160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-735" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1290" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabla_variedades" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">tabla_variedades!$A$1:$H$1356</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">tabla_variedades!$A$1:$H$1366</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5315" uniqueCount="1424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5319" uniqueCount="1426">
   <si>
     <t>id</t>
   </si>
@@ -4295,6 +4295,12 @@
   </si>
   <si>
     <t>2007</t>
+  </si>
+  <si>
+    <t>2422</t>
+  </si>
+  <si>
+    <t>DAMASCUS_</t>
   </si>
 </sst>
 </file>
@@ -5147,7 +5153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1366"/>
+  <dimension ref="A1:H1367"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="11.42578125" style="1"/>
@@ -6135,7 +6141,7 @@
         <v>2049</v>
       </c>
       <c r="G38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -6811,7 +6817,7 @@
         <v>2341</v>
       </c>
       <c r="G64">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -8293,7 +8299,7 @@
         <v>2299</v>
       </c>
       <c r="G121">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H121">
         <v>1</v>
@@ -8943,7 +8949,7 @@
         <v>2264</v>
       </c>
       <c r="G146">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H146" t="s">
         <v>11</v>
@@ -16951,7 +16957,7 @@
         <v>5941</v>
       </c>
       <c r="G454">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H454" t="s">
         <v>11</v>
@@ -24543,7 +24549,7 @@
         <v>0</v>
       </c>
       <c r="G746">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H746" t="s">
         <v>11</v>
@@ -28313,7 +28319,7 @@
         <v>0</v>
       </c>
       <c r="G891">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H891" t="s">
         <v>11</v>
@@ -29546,7 +29552,7 @@
         <v>938</v>
       </c>
       <c r="B939" t="s">
-        <v>950</v>
+        <v>1425</v>
       </c>
       <c r="C939" t="s">
         <v>9</v>
@@ -33539,7 +33545,7 @@
         <v>0</v>
       </c>
       <c r="G1092">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H1092" t="s">
         <v>11</v>
@@ -39051,7 +39057,7 @@
         <v>2430</v>
       </c>
       <c r="G1304">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1304">
         <v>1</v>
@@ -39103,7 +39109,7 @@
         <v>2424</v>
       </c>
       <c r="G1306">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1306">
         <v>1</v>
@@ -39207,7 +39213,7 @@
         <v>2426</v>
       </c>
       <c r="G1310">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1310">
         <v>1</v>
@@ -40400,10 +40406,10 @@
         <v>2440</v>
       </c>
       <c r="G1356">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H1356">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1357" spans="1:8" x14ac:dyDescent="0.25">
@@ -40423,10 +40429,10 @@
         <v>1413</v>
       </c>
       <c r="G1357">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H1357">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1358" spans="1:8" x14ac:dyDescent="0.25">
@@ -40446,10 +40452,10 @@
         <v>1414</v>
       </c>
       <c r="G1358">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H1358">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1359" spans="1:8" x14ac:dyDescent="0.25">
@@ -40469,10 +40475,10 @@
         <v>1415</v>
       </c>
       <c r="G1359">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H1359">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1360" spans="1:8" x14ac:dyDescent="0.25">
@@ -40492,10 +40498,10 @@
         <v>1416</v>
       </c>
       <c r="G1360">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H1360">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1361" spans="2:8" x14ac:dyDescent="0.25">
@@ -40515,10 +40521,10 @@
         <v>1417</v>
       </c>
       <c r="G1361">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H1361">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1362" spans="2:8" x14ac:dyDescent="0.25">
@@ -40538,10 +40544,10 @@
         <v>1418</v>
       </c>
       <c r="G1362">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H1362">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1363" spans="2:8" x14ac:dyDescent="0.25">
@@ -40561,10 +40567,10 @@
         <v>1419</v>
       </c>
       <c r="G1363">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H1363">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1364" spans="2:8" x14ac:dyDescent="0.25">
@@ -40584,10 +40590,10 @@
         <v>1420</v>
       </c>
       <c r="G1364">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H1364">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1365" spans="2:8" x14ac:dyDescent="0.25">
@@ -40607,10 +40613,10 @@
         <v>1421</v>
       </c>
       <c r="G1365">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H1365">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1366" spans="2:8" x14ac:dyDescent="0.25">
@@ -40630,14 +40636,37 @@
         <v>1423</v>
       </c>
       <c r="G1366">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H1366">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1367" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1367" t="s">
+        <v>950</v>
+      </c>
+      <c r="C1367" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1367" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1367">
+        <v>26</v>
+      </c>
+      <c r="F1367" s="1" t="s">
+        <v>1424</v>
+      </c>
+      <c r="G1367">
+        <v>1</v>
+      </c>
+      <c r="H1367">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1356" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H1366" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/archivos/tabla_variedades.xlsx
+++ b/archivos/tabla_variedades.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTICA\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969D51BC-FF0F-4EBF-A690-459F569BA160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0E35C2-4E98-4DC7-B5A6-FA0ABB7E2F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1290" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabla_variedades" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">tabla_variedades!$A$1:$H$1366</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">tabla_variedades!$A$1:$H$1374</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5319" uniqueCount="1426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5347" uniqueCount="1434">
   <si>
     <t>id</t>
   </si>
@@ -4301,6 +4301,30 @@
   </si>
   <si>
     <t>DAMASCUS_</t>
+  </si>
+  <si>
+    <t>MOONPHASE</t>
+  </si>
+  <si>
+    <t>ORANGE PARTY</t>
+  </si>
+  <si>
+    <t>PROGRESS</t>
+  </si>
+  <si>
+    <t>BLUEBERRY</t>
+  </si>
+  <si>
+    <t>TIGER</t>
+  </si>
+  <si>
+    <t>MISS FRANCE</t>
+  </si>
+  <si>
+    <t>CREME CARAMEL</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
@@ -5153,7 +5177,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1367"/>
+  <dimension ref="A1:H1374"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="11.42578125" style="1"/>
@@ -8943,7 +8967,7 @@
         <v>17</v>
       </c>
       <c r="E146">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F146">
         <v>2264</v>
@@ -24543,7 +24567,7 @@
         <v>17</v>
       </c>
       <c r="E746">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F746">
         <v>0</v>
@@ -39213,7 +39237,7 @@
         <v>2426</v>
       </c>
       <c r="G1310">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1310">
         <v>1</v>
@@ -40665,8 +40689,169 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1368" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1368" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C1368" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1368" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1368">
+        <v>0</v>
+      </c>
+      <c r="F1368" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G1368">
+        <v>8</v>
+      </c>
+      <c r="H1368">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1369" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1369" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C1369" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1369" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1369">
+        <v>0</v>
+      </c>
+      <c r="F1369" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G1369">
+        <v>8</v>
+      </c>
+      <c r="H1369">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1370" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1370" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C1370" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1370" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1370">
+        <v>0</v>
+      </c>
+      <c r="F1370" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G1370">
+        <v>8</v>
+      </c>
+      <c r="H1370">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1371" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1371" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C1371" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1371" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1371">
+        <v>0</v>
+      </c>
+      <c r="F1371" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G1371">
+        <v>8</v>
+      </c>
+      <c r="H1371">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1372" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1372" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C1372" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1372" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1372">
+        <v>0</v>
+      </c>
+      <c r="F1372" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G1372">
+        <v>8</v>
+      </c>
+      <c r="H1372">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1373" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1373" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C1373" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1373" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1373">
+        <v>0</v>
+      </c>
+      <c r="F1373" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G1373">
+        <v>8</v>
+      </c>
+      <c r="H1373">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1374" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1374" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C1374" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1374" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1374">
+        <v>0</v>
+      </c>
+      <c r="F1374" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G1374">
+        <v>8</v>
+      </c>
+      <c r="H1374">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1366" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H1374" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/archivos/tabla_variedades.xlsx
+++ b/archivos/tabla_variedades.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTICA\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0E35C2-4E98-4DC7-B5A6-FA0ABB7E2F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7443A5B3-9963-48B4-AC2F-DA3C4C528740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1290" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabla_variedades" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">tabla_variedades!$A$1:$H$1374</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">tabla_variedades!$A$1:$H$1414</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5347" uniqueCount="1434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5515" uniqueCount="1476">
   <si>
     <t>id</t>
   </si>
@@ -4325,6 +4325,132 @@
   </si>
   <si>
     <t>0</t>
+  </si>
+  <si>
+    <t>KEDALL</t>
+  </si>
+  <si>
+    <t>SUGAR MORNING</t>
+  </si>
+  <si>
+    <t>SHIRO (L-623)</t>
+  </si>
+  <si>
+    <t>AURA</t>
+  </si>
+  <si>
+    <t>KASIA</t>
+  </si>
+  <si>
+    <t>BACCARDI</t>
+  </si>
+  <si>
+    <t>CECILIA</t>
+  </si>
+  <si>
+    <t>ZM - 167 - FJA</t>
+  </si>
+  <si>
+    <t>M - 633</t>
+  </si>
+  <si>
+    <t>CERASUS</t>
+  </si>
+  <si>
+    <t>MOCHI</t>
+  </si>
+  <si>
+    <t>L - 131</t>
+  </si>
+  <si>
+    <t>LAMBRETTA</t>
+  </si>
+  <si>
+    <t>CHERRY MARVEL</t>
+  </si>
+  <si>
+    <t>ALLEGRETTO</t>
+  </si>
+  <si>
+    <t>CHARITO (K-541)</t>
+  </si>
+  <si>
+    <t>NP - 251 - FB</t>
+  </si>
+  <si>
+    <t>BABY DOLPHIN</t>
+  </si>
+  <si>
+    <t>NEW ROXANNE</t>
+  </si>
+  <si>
+    <t>CHARISMA</t>
+  </si>
+  <si>
+    <t>VAMPIRE</t>
+  </si>
+  <si>
+    <t>SAUVAGE</t>
+  </si>
+  <si>
+    <t>GREEN PISTACHO</t>
+  </si>
+  <si>
+    <t>2021 VE 5</t>
+  </si>
+  <si>
+    <t>PISTACHO (K-444)</t>
+  </si>
+  <si>
+    <t>M - 095</t>
+  </si>
+  <si>
+    <t>M - 392</t>
+  </si>
+  <si>
+    <t>YELLOWSTONE</t>
+  </si>
+  <si>
+    <t>DIAMANTE</t>
+  </si>
+  <si>
+    <t>DC - 181016</t>
+  </si>
+  <si>
+    <t>L - 157</t>
+  </si>
+  <si>
+    <t>DCM 2019 - 9030</t>
+  </si>
+  <si>
+    <t>ETERNAL LOVE</t>
+  </si>
+  <si>
+    <t>TESORO PURPURA</t>
+  </si>
+  <si>
+    <t>OPERETTA</t>
+  </si>
+  <si>
+    <t>L - 247</t>
+  </si>
+  <si>
+    <t>EXPERT</t>
+  </si>
+  <si>
+    <t>EMERALD</t>
+  </si>
+  <si>
+    <t>DCS - 2021 - 2557</t>
+  </si>
+  <si>
+    <t>DTC - 206039</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>DAMINA</t>
   </si>
 </sst>
 </file>
@@ -5177,7 +5303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1374"/>
+  <dimension ref="A1:H1416"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="11.42578125" style="1"/>
@@ -13329,7 +13455,7 @@
         <v>357</v>
       </c>
       <c r="C314" t="s">
-        <v>295</v>
+        <v>23</v>
       </c>
       <c r="D314" t="s">
         <v>48</v>
@@ -38549,7 +38675,7 @@
         <v>1282</v>
       </c>
       <c r="C1284" t="s">
-        <v>295</v>
+        <v>23</v>
       </c>
       <c r="D1284" t="s">
         <v>278</v>
@@ -40850,8 +40976,974 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1375" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1375" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C1375" t="s">
+        <v>295</v>
+      </c>
+      <c r="D1375" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1375">
+        <v>0</v>
+      </c>
+      <c r="F1375">
+        <v>0</v>
+      </c>
+      <c r="G1375">
+        <v>8</v>
+      </c>
+      <c r="H1375" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1376" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1376" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C1376" t="s">
+        <v>295</v>
+      </c>
+      <c r="D1376" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1376">
+        <v>0</v>
+      </c>
+      <c r="F1376">
+        <v>0</v>
+      </c>
+      <c r="G1376">
+        <v>8</v>
+      </c>
+      <c r="H1376" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1377" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1377" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C1377" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1377" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1377">
+        <v>0</v>
+      </c>
+      <c r="F1377">
+        <v>0</v>
+      </c>
+      <c r="G1377">
+        <v>8</v>
+      </c>
+      <c r="H1377" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1378" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1378" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C1378" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1378" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1378">
+        <v>0</v>
+      </c>
+      <c r="F1378">
+        <v>0</v>
+      </c>
+      <c r="G1378">
+        <v>8</v>
+      </c>
+      <c r="H1378" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1379" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1379" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C1379" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1379" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1379">
+        <v>0</v>
+      </c>
+      <c r="F1379">
+        <v>0</v>
+      </c>
+      <c r="G1379">
+        <v>8</v>
+      </c>
+      <c r="H1379" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1380" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1380" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C1380" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1380" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1380">
+        <v>0</v>
+      </c>
+      <c r="F1380">
+        <v>0</v>
+      </c>
+      <c r="G1380">
+        <v>8</v>
+      </c>
+      <c r="H1380" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1381" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1381" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C1381" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1381" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1381">
+        <v>0</v>
+      </c>
+      <c r="F1381">
+        <v>0</v>
+      </c>
+      <c r="G1381">
+        <v>8</v>
+      </c>
+      <c r="H1381" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1382" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1382" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C1382" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1382" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1382">
+        <v>0</v>
+      </c>
+      <c r="F1382">
+        <v>0</v>
+      </c>
+      <c r="G1382">
+        <v>8</v>
+      </c>
+      <c r="H1382" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1383" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1383" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C1383" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1383" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1383">
+        <v>0</v>
+      </c>
+      <c r="F1383">
+        <v>0</v>
+      </c>
+      <c r="G1383">
+        <v>8</v>
+      </c>
+      <c r="H1383" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1384" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1384" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C1384" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1384" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1384">
+        <v>0</v>
+      </c>
+      <c r="F1384">
+        <v>0</v>
+      </c>
+      <c r="G1384">
+        <v>8</v>
+      </c>
+      <c r="H1384" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1385" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1385" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C1385" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1385" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1385">
+        <v>0</v>
+      </c>
+      <c r="F1385">
+        <v>0</v>
+      </c>
+      <c r="G1385">
+        <v>8</v>
+      </c>
+      <c r="H1385" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1386" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1386" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C1386" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1386" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1386">
+        <v>0</v>
+      </c>
+      <c r="F1386">
+        <v>0</v>
+      </c>
+      <c r="G1386">
+        <v>8</v>
+      </c>
+      <c r="H1386" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1387" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1387" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C1387" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1387" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1387">
+        <v>0</v>
+      </c>
+      <c r="F1387">
+        <v>0</v>
+      </c>
+      <c r="G1387">
+        <v>8</v>
+      </c>
+      <c r="H1387" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1388" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1388" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C1388" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1388" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1388">
+        <v>0</v>
+      </c>
+      <c r="F1388">
+        <v>0</v>
+      </c>
+      <c r="G1388">
+        <v>8</v>
+      </c>
+      <c r="H1388" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1389" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1389" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C1389" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1389" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1389">
+        <v>0</v>
+      </c>
+      <c r="F1389">
+        <v>0</v>
+      </c>
+      <c r="G1389">
+        <v>8</v>
+      </c>
+      <c r="H1389" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1390" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1390" t="s">
+        <v>1470</v>
+      </c>
+      <c r="C1390" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1390" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1390">
+        <v>0</v>
+      </c>
+      <c r="F1390">
+        <v>0</v>
+      </c>
+      <c r="G1390">
+        <v>8</v>
+      </c>
+      <c r="H1390" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1391" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1391" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C1391" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1391" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1391">
+        <v>0</v>
+      </c>
+      <c r="F1391">
+        <v>0</v>
+      </c>
+      <c r="G1391">
+        <v>8</v>
+      </c>
+      <c r="H1391" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1392" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1392" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C1392" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1392" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1392">
+        <v>0</v>
+      </c>
+      <c r="F1392">
+        <v>0</v>
+      </c>
+      <c r="G1392">
+        <v>8</v>
+      </c>
+      <c r="H1392" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1393" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1393" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C1393" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1393" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1393">
+        <v>0</v>
+      </c>
+      <c r="F1393">
+        <v>0</v>
+      </c>
+      <c r="G1393">
+        <v>8</v>
+      </c>
+      <c r="H1393" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1394" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1394" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C1394" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1394" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1394">
+        <v>0</v>
+      </c>
+      <c r="F1394">
+        <v>0</v>
+      </c>
+      <c r="G1394">
+        <v>8</v>
+      </c>
+      <c r="H1394" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1395" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1395" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C1395" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1395" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1395">
+        <v>0</v>
+      </c>
+      <c r="F1395">
+        <v>0</v>
+      </c>
+      <c r="G1395">
+        <v>8</v>
+      </c>
+      <c r="H1395" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1396" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1396" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C1396" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1396" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1396">
+        <v>0</v>
+      </c>
+      <c r="F1396">
+        <v>0</v>
+      </c>
+      <c r="G1396">
+        <v>8</v>
+      </c>
+      <c r="H1396" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1397" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1397" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C1397" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1397" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1397">
+        <v>0</v>
+      </c>
+      <c r="F1397">
+        <v>0</v>
+      </c>
+      <c r="G1397">
+        <v>8</v>
+      </c>
+      <c r="H1397" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1398" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1398" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C1398" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1398" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1398">
+        <v>0</v>
+      </c>
+      <c r="F1398">
+        <v>0</v>
+      </c>
+      <c r="G1398">
+        <v>8</v>
+      </c>
+      <c r="H1398" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1399" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1399" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C1399" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1399" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1399">
+        <v>0</v>
+      </c>
+      <c r="F1399">
+        <v>0</v>
+      </c>
+      <c r="G1399">
+        <v>8</v>
+      </c>
+      <c r="H1399" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1400" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1400" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C1400" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1400" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1400">
+        <v>0</v>
+      </c>
+      <c r="F1400">
+        <v>0</v>
+      </c>
+      <c r="G1400">
+        <v>8</v>
+      </c>
+      <c r="H1400" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1401" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1401" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C1401" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1401" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1401">
+        <v>0</v>
+      </c>
+      <c r="F1401">
+        <v>0</v>
+      </c>
+      <c r="G1401">
+        <v>8</v>
+      </c>
+      <c r="H1401" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1402" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1402" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C1402" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1402" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1402">
+        <v>0</v>
+      </c>
+      <c r="F1402">
+        <v>0</v>
+      </c>
+      <c r="G1402">
+        <v>8</v>
+      </c>
+      <c r="H1402" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1403" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1403" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C1403" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1403" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1403">
+        <v>0</v>
+      </c>
+      <c r="F1403">
+        <v>0</v>
+      </c>
+      <c r="G1403">
+        <v>8</v>
+      </c>
+      <c r="H1403" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1404" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1404" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C1404" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1404" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1404">
+        <v>0</v>
+      </c>
+      <c r="F1404">
+        <v>0</v>
+      </c>
+      <c r="G1404">
+        <v>8</v>
+      </c>
+      <c r="H1404" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1405" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1405" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C1405" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1405" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1405">
+        <v>0</v>
+      </c>
+      <c r="F1405">
+        <v>0</v>
+      </c>
+      <c r="G1405">
+        <v>8</v>
+      </c>
+      <c r="H1405" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1406" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1406" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C1406" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1406" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1406">
+        <v>0</v>
+      </c>
+      <c r="F1406">
+        <v>0</v>
+      </c>
+      <c r="G1406">
+        <v>8</v>
+      </c>
+      <c r="H1406" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1407" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1407" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C1407" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1407" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1407">
+        <v>0</v>
+      </c>
+      <c r="F1407">
+        <v>0</v>
+      </c>
+      <c r="G1407">
+        <v>8</v>
+      </c>
+      <c r="H1407" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1408" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1408" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C1408" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1408" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1408">
+        <v>0</v>
+      </c>
+      <c r="F1408">
+        <v>0</v>
+      </c>
+      <c r="G1408">
+        <v>8</v>
+      </c>
+      <c r="H1408" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1409" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1409" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C1409" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1409" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1409">
+        <v>0</v>
+      </c>
+      <c r="F1409">
+        <v>0</v>
+      </c>
+      <c r="G1409">
+        <v>8</v>
+      </c>
+      <c r="H1409" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1410" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1410" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C1410" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1410" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1410">
+        <v>0</v>
+      </c>
+      <c r="F1410">
+        <v>0</v>
+      </c>
+      <c r="G1410">
+        <v>8</v>
+      </c>
+      <c r="H1410" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1411" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1411" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C1411" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1411" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1411">
+        <v>0</v>
+      </c>
+      <c r="F1411">
+        <v>0</v>
+      </c>
+      <c r="G1411">
+        <v>8</v>
+      </c>
+      <c r="H1411" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1412" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1412" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C1412" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1412" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1412">
+        <v>0</v>
+      </c>
+      <c r="F1412">
+        <v>0</v>
+      </c>
+      <c r="G1412">
+        <v>8</v>
+      </c>
+      <c r="H1412" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1413" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1413" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C1413" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1413" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1413">
+        <v>0</v>
+      </c>
+      <c r="F1413">
+        <v>0</v>
+      </c>
+      <c r="G1413">
+        <v>8</v>
+      </c>
+      <c r="H1413" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1414" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1414" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C1414" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1414" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1414">
+        <v>0</v>
+      </c>
+      <c r="F1414">
+        <v>0</v>
+      </c>
+      <c r="G1414">
+        <v>8</v>
+      </c>
+      <c r="H1414" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1415" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1415" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C1415" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1415" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1415">
+        <v>0</v>
+      </c>
+      <c r="F1415">
+        <v>0</v>
+      </c>
+      <c r="G1415">
+        <v>8</v>
+      </c>
+      <c r="H1415" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1416" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1416" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C1416" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1416" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1416">
+        <v>0</v>
+      </c>
+      <c r="F1416">
+        <v>0</v>
+      </c>
+      <c r="G1416">
+        <v>8</v>
+      </c>
+      <c r="H1416" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1374" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H1414" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
